--- a/data/Indicadores de Qualidade/Indicadores_Qualidade_2026.xlsx
+++ b/data/Indicadores de Qualidade/Indicadores_Qualidade_2026.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="EstaPasta_de_trabalho"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\SGQ\INDICADORES\QUALIDADE\ELOHIM\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Manutencao\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03ECD2B4-D8A4-4B1D-A389-1D3BC2FB08AD}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="915" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" tabRatio="915"/>
   </bookViews>
   <sheets>
     <sheet name="MENU PRINCIPAL" sheetId="36" r:id="rId1"/>
@@ -56,7 +55,7 @@
     <definedName name="Excel_BuiltIn_Print_Area_9" localSheetId="4">#REF!</definedName>
     <definedName name="Excel_BuiltIn_Print_Area_9">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -345,7 +344,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="9">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(&quot;R$ &quot;* #,##0.00_);_(&quot;R$ &quot;* \(#,##0.00\);_(&quot;R$ &quot;* &quot;-&quot;??_);_(@_)"/>
@@ -1561,6 +1560,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1643,8 +1643,11 @@
                 <c:pt idx="3">
                   <c:v>1920.5</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
                 <c:pt idx="12">
-                  <c:v>69588.44</c:v>
+                  <c:v>69758.44</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1729,6 +1732,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1811,8 +1815,11 @@
                 <c:pt idx="3">
                   <c:v>3443.73</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>1260.23</c:v>
+                </c:pt>
                 <c:pt idx="12">
-                  <c:v>11390.06</c:v>
+                  <c:v>12650.289999999999</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2044,6 +2051,10 @@
               <a:rPr lang="pt-BR" sz="1400"/>
               <a:t>Produto Não Conforme - Rejeição Externa</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t/>
+            </a:r>
             <a:br>
               <a:rPr lang="pt-BR"/>
             </a:br>
@@ -2240,6 +2251,9 @@
                 <c:pt idx="3">
                   <c:v>666</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2418,7 +2432,7 @@
                   <c:v>2269.189175</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>2211.8907750000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -2766,6 +2780,9 @@
                 <c:pt idx="3">
                   <c:v>1572.66</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>495.99</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2807,6 +2824,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1254.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2952,7 +2972,7 @@
                   <c:v>4538.37835</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4423.7815500000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -3384,8 +3404,11 @@
                 <c:pt idx="3">
                   <c:v>2827.16</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>665.99</c:v>
+                </c:pt>
                 <c:pt idx="12">
-                  <c:v>46862.16</c:v>
+                  <c:v>47528.15</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3653,6 +3676,9 @@
                 <c:pt idx="3">
                   <c:v>1572.66</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>495.99</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3796,7 +3822,7 @@
                   <c:v>4538.37835</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4423.7815500000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -4122,6 +4148,9 @@
                 <c:pt idx="3">
                   <c:v>1254.5</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -4265,7 +4294,7 @@
                   <c:v>4538.37835</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4423.7815500000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -5344,8 +5373,68 @@
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
                 <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>0</c:v>
+                </c:pt>
                 <c:pt idx="20">
-                  <c:v>0</c:v>
+                  <c:v>35</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6592,16 +6681,16 @@
                   <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>23</c:v>
+                  <c:v>25</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>0</c:v>
@@ -6610,13 +6699,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>153</c:v>
+                  <c:v>158</c:v>
                 </c:pt>
                 <c:pt idx="11">
                   <c:v>2</c:v>
@@ -6625,13 +6714,13 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>34</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>138</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>12</c:v>
+                  <c:v>29</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>0</c:v>
@@ -7170,7 +7259,7 @@
                   <c:v>2.7302174919018974E-2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>6.901991717609939E-3</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -7194,7 +7283,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.0000%">
-                  <c:v>2.8371230335920861E-2</c:v>
+                  <c:v>2.2824536376604851E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7832,7 +7921,7 @@
                 <c:formatCode>0.00%</c:formatCode>
                 <c:ptCount val="13"/>
                 <c:pt idx="0">
-                  <c:v>5.0517807527153326E-4</c:v>
+                  <c:v>3.0310684516291994E-3</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>0</c:v>
@@ -7844,7 +7933,7 @@
                   <c:v>7.8667283664969924E-3</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>3.9439952672056793E-2</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -7868,7 +7957,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12" formatCode="0.000%">
-                  <c:v>4.6712921618465341E-3</c:v>
+                  <c:v>1.4163439983696759E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8433,7 +8522,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>56</c:v>
+                  <c:v>66</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>0</c:v>
@@ -8460,10 +8549,10 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11</c:v>
+                  <c:v>211</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>68</c:v>
+                  <c:v>278</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8743,6 +8832,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -8823,6 +8913,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>3443.73</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1260.23</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9289,7 +9382,7 @@
                   <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>12</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -9313,7 +9406,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>29</c:v>
+                  <c:v>41</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9455,6 +9548,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9462,7 +9556,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -9781,7 +9874,7 @@
                   <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -9805,7 +9898,7 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>6</c:v>
+                  <c:v>7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -9947,6 +10040,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -9954,7 +10048,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -10036,6 +10129,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -10133,6 +10227,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -10212,6 +10307,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1920.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10634,6 +10732,9 @@
                 <c:pt idx="3">
                   <c:v>1920.5</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>170</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10787,6 +10888,9 @@
                 <c:pt idx="3">
                   <c:v>3443.73</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>1260.23</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -10902,7 +11006,7 @@
                   <c:v>4538.37835</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>4423.7815500000006</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -11374,6 +11478,9 @@
                 <c:pt idx="3">
                   <c:v>0</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
+                </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
                 </c:pt>
@@ -11593,6 +11700,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -11693,6 +11801,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -11729,7 +11838,7 @@
                 <c:formatCode>_(* #,##0.00_);_(* \(#,##0.00\);_(* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>80978.5</c:v>
+                  <c:v>82408.73</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11939,6 +12048,10 @@
               <a:rPr lang="pt-BR" sz="1400"/>
               <a:t>Produto Não Conforme - Rejeição Total</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t/>
+            </a:r>
             <a:br>
               <a:rPr lang="pt-BR"/>
             </a:br>
@@ -12100,6 +12213,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -12134,6 +12248,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1871.07</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>764.24</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12242,6 +12359,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -12276,6 +12394,9 @@
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>666</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12375,6 +12496,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -12456,7 +12578,7 @@
                   <c:v>2269.189175</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>2211.8907750000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -12733,6 +12855,7 @@
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -12843,6 +12966,7 @@
                     <a:noFill/>
                   </a:ln>
                 </c15:spPr>
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -12925,8 +13049,11 @@
                 <c:pt idx="3">
                   <c:v>2537.0699999999997</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>764.24</c:v>
+                </c:pt>
                 <c:pt idx="12">
-                  <c:v>33716.339999999997</c:v>
+                  <c:v>34480.579999999994</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -13114,6 +13241,10 @@
               <a:rPr lang="pt-BR" sz="1400"/>
               <a:t>Produto Não Conforme - Rejeição Interna</a:t>
             </a:r>
+            <a:r>
+              <a:rPr lang="pt-BR"/>
+              <a:t/>
+            </a:r>
             <a:br>
               <a:rPr lang="pt-BR"/>
             </a:br>
@@ -13310,6 +13441,9 @@
                 <c:pt idx="3">
                   <c:v>1871.07</c:v>
                 </c:pt>
+                <c:pt idx="4">
+                  <c:v>764.24</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -13488,7 +13622,7 @@
                   <c:v>2269.189175</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0</c:v>
+                  <c:v>2211.8907750000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>0</c:v>
@@ -30110,7 +30244,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
@@ -31744,7 +31878,7 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
@@ -31857,12 +31991,18 @@
       <c r="B9" s="161" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="161"/>
-      <c r="D9" s="161"/>
-      <c r="E9" s="161"/>
+      <c r="C9" s="161">
+        <v>0</v>
+      </c>
+      <c r="D9" s="161">
+        <v>0</v>
+      </c>
+      <c r="E9" s="161">
+        <v>1</v>
+      </c>
       <c r="F9" s="162">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -31963,11 +32103,11 @@
       </c>
       <c r="E17" s="161">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="162">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -31980,7 +32120,7 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF00B0F0"/>
   </sheetPr>
@@ -32056,9 +32196,13 @@
       <c r="B7" s="71">
         <v>46143</v>
       </c>
-      <c r="C7" s="72"/>
+      <c r="C7" s="72">
+        <v>884756.31</v>
+      </c>
       <c r="D7" s="4"/>
-      <c r="E7" s="77"/>
+      <c r="E7" s="77">
+        <v>5071</v>
+      </c>
     </row>
     <row r="8" spans="2:5" ht="15.75" x14ac:dyDescent="0.2">
       <c r="B8" s="71">
@@ -32127,7 +32271,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
@@ -32306,11 +32450,15 @@
       <c r="A7" s="115">
         <v>46143</v>
       </c>
-      <c r="B7" s="116"/>
-      <c r="C7" s="116"/>
+      <c r="B7" s="116">
+        <v>170</v>
+      </c>
+      <c r="C7" s="116">
+        <v>1260.23</v>
+      </c>
       <c r="D7" s="116">
         <f>DADOS!C7*0.5%</f>
-        <v>0</v>
+        <v>4423.7815500000006</v>
       </c>
       <c r="E7" s="184"/>
       <c r="F7" s="4"/>
@@ -32468,11 +32616,11 @@
       </c>
       <c r="B15" s="116">
         <f>SUM(B3:B14)</f>
-        <v>69588.44</v>
+        <v>69758.44</v>
       </c>
       <c r="C15" s="116">
         <f>SUM(C3:C14)</f>
-        <v>11390.06</v>
+        <v>12650.289999999999</v>
       </c>
       <c r="D15" s="181" t="s">
         <v>65</v>
@@ -32992,7 +33140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
@@ -33129,7 +33277,9 @@
       <c r="A7" s="125">
         <v>46143</v>
       </c>
-      <c r="B7" s="126"/>
+      <c r="B7" s="126">
+        <v>0</v>
+      </c>
       <c r="C7" s="127"/>
       <c r="D7" s="130"/>
       <c r="E7" s="128"/>
@@ -33415,7 +33565,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
@@ -33511,11 +33661,11 @@
       </c>
       <c r="B7" s="58">
         <f>'Custo NC '!B7</f>
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="C7" s="58">
         <f>'Custo NC '!C7</f>
-        <v>0</v>
+        <v>1260.23</v>
       </c>
       <c r="N7" s="52"/>
     </row>
@@ -33623,11 +33773,11 @@
       </c>
       <c r="B15" s="58">
         <f>'Custo NC '!B15</f>
-        <v>69588.44</v>
+        <v>69758.44</v>
       </c>
       <c r="C15" s="58">
         <f>'Custo NC '!C15</f>
-        <v>11390.06</v>
+        <v>12650.289999999999</v>
       </c>
       <c r="N15" s="52"/>
     </row>
@@ -33637,7 +33787,7 @@
       </c>
       <c r="B16" s="61">
         <f>SUM(B15:C15)</f>
-        <v>80978.5</v>
+        <v>82408.73</v>
       </c>
       <c r="C16" s="62"/>
       <c r="D16" s="54"/>
@@ -33660,7 +33810,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
@@ -33818,7 +33968,7 @@
         <v>46054</v>
       </c>
       <c r="B5" s="101">
-        <f t="shared" ref="B5:B7" si="0">SUM(C5:D5)</f>
+        <f t="shared" ref="B5:B8" si="0">SUM(C5:D5)</f>
         <v>0</v>
       </c>
       <c r="C5" s="101">
@@ -33947,19 +34097,26 @@
       <c r="A8" s="68">
         <v>46143</v>
       </c>
-      <c r="B8" s="101"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="101"/>
+      <c r="B8" s="101">
+        <f t="shared" si="0"/>
+        <v>764.24</v>
+      </c>
+      <c r="C8" s="101">
+        <v>764.24</v>
+      </c>
+      <c r="D8" s="101">
+        <v>0</v>
+      </c>
       <c r="E8" s="178">
         <v>2.5000000000000001E-3</v>
       </c>
       <c r="F8" s="147">
         <f>DADOS!C7</f>
-        <v>0</v>
+        <v>884756.31</v>
       </c>
       <c r="G8" s="146">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2211.8907750000003</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="4"/>
@@ -34237,11 +34394,11 @@
       </c>
       <c r="B16" s="101">
         <f>SUM(B4:B15)</f>
-        <v>33716.339999999997</v>
+        <v>34480.579999999994</v>
       </c>
       <c r="C16" s="101">
         <f t="shared" ref="C16:D16" si="2">SUM(C4:C15)</f>
-        <v>5974.96</v>
+        <v>6739.2</v>
       </c>
       <c r="D16" s="101">
         <f t="shared" si="2"/>
@@ -35271,7 +35428,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Plan6">
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
@@ -35407,7 +35564,7 @@
         <v>46054</v>
       </c>
       <c r="B5" s="17">
-        <f t="shared" ref="B5:B7" si="0">SUM(C5:D5)</f>
+        <f t="shared" ref="B5:B8" si="0">SUM(C5:D5)</f>
         <v>465</v>
       </c>
       <c r="C5" s="17">
@@ -35503,19 +35660,26 @@
       <c r="A8" s="65">
         <v>46143</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
+      <c r="B8" s="17">
+        <f t="shared" si="0"/>
+        <v>665.99</v>
+      </c>
+      <c r="C8" s="17">
+        <v>495.99</v>
+      </c>
+      <c r="D8" s="17">
+        <v>170</v>
+      </c>
       <c r="E8" s="177">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="F8" s="98">
         <f>DADOS!C7</f>
-        <v>0</v>
+        <v>884756.31</v>
       </c>
       <c r="G8" s="145">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>4423.7815500000006</v>
       </c>
       <c r="H8" s="90"/>
       <c r="I8" s="4"/>
@@ -35705,15 +35869,15 @@
       </c>
       <c r="B16" s="17">
         <f>SUM(B4:B15)</f>
-        <v>46862.16</v>
+        <v>47528.15</v>
       </c>
       <c r="C16" s="17">
         <f>SUM(C4:C15)</f>
-        <v>5415.0999999999995</v>
+        <v>5911.0899999999992</v>
       </c>
       <c r="D16" s="17">
         <f t="shared" ref="D16" si="2">SUM(D4:D15)</f>
-        <v>41447.06</v>
+        <v>41617.06</v>
       </c>
       <c r="E16" s="100"/>
       <c r="F16" s="100"/>
@@ -36263,7 +36427,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
@@ -36765,40 +36929,80 @@
       <c r="A8" s="110">
         <v>46143</v>
       </c>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="107"/>
-      <c r="K8" s="107"/>
-      <c r="L8" s="107"/>
-      <c r="M8" s="107"/>
-      <c r="N8" s="107"/>
-      <c r="O8" s="107"/>
-      <c r="P8" s="107"/>
-      <c r="Q8" s="107"/>
-      <c r="R8" s="107"/>
-      <c r="S8" s="107"/>
-      <c r="T8" s="107"/>
-      <c r="U8" s="107"/>
+      <c r="B8" s="107">
+        <v>0</v>
+      </c>
+      <c r="C8" s="107">
+        <v>0</v>
+      </c>
+      <c r="D8" s="107">
+        <v>1</v>
+      </c>
+      <c r="E8" s="107">
+        <v>2</v>
+      </c>
+      <c r="F8" s="102">
+        <v>0</v>
+      </c>
+      <c r="G8" s="107">
+        <v>2</v>
+      </c>
+      <c r="H8" s="102">
+        <v>0</v>
+      </c>
+      <c r="I8" s="102">
+        <v>0</v>
+      </c>
+      <c r="J8" s="107">
+        <v>1</v>
+      </c>
+      <c r="K8" s="107">
+        <v>0</v>
+      </c>
+      <c r="L8" s="107">
+        <v>5</v>
+      </c>
+      <c r="M8" s="107">
+        <v>0</v>
+      </c>
+      <c r="N8" s="107">
+        <v>0</v>
+      </c>
+      <c r="O8" s="107">
+        <v>7</v>
+      </c>
+      <c r="P8" s="107">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="107">
+        <v>17</v>
+      </c>
+      <c r="R8" s="107">
+        <v>0</v>
+      </c>
+      <c r="S8" s="102">
+        <v>0</v>
+      </c>
+      <c r="T8" s="102">
+        <v>0</v>
+      </c>
+      <c r="U8" s="107">
+        <v>0</v>
+      </c>
       <c r="V8" s="171">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="W8" s="172" t="e">
+        <v>35</v>
+      </c>
+      <c r="W8" s="172">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>6.901991717609939E-3</v>
       </c>
       <c r="X8" s="173">
         <v>0.01</v>
       </c>
       <c r="Y8" s="174">
         <f>DADOS!E7</f>
-        <v>0</v>
+        <v>5071</v>
       </c>
       <c r="Z8" s="167"/>
       <c r="AA8" s="51"/>
@@ -37119,11 +37323,11 @@
       </c>
       <c r="D16" s="85">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" s="85">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F16" s="85">
         <f t="shared" si="2"/>
@@ -37131,7 +37335,7 @@
       </c>
       <c r="G16" s="85">
         <f t="shared" si="2"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H16" s="85">
         <f t="shared" si="2"/>
@@ -37143,7 +37347,7 @@
       </c>
       <c r="J16" s="85">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" s="85">
         <f t="shared" si="2"/>
@@ -37151,7 +37355,7 @@
       </c>
       <c r="L16" s="85">
         <f t="shared" si="2"/>
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="M16" s="85">
         <f t="shared" si="2"/>
@@ -37163,7 +37367,7 @@
       </c>
       <c r="O16" s="85">
         <f t="shared" si="2"/>
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="P16" s="85">
         <f t="shared" si="2"/>
@@ -37171,7 +37375,7 @@
       </c>
       <c r="Q16" s="85">
         <f t="shared" si="2"/>
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="R16" s="85">
         <f t="shared" si="2"/>
@@ -37191,18 +37395,18 @@
       </c>
       <c r="V16" s="171">
         <f t="shared" ref="V16" si="3">SUM(V4:V15)</f>
-        <v>413</v>
+        <v>448</v>
       </c>
       <c r="W16" s="175">
         <f>SUM(V16/Y16)</f>
-        <v>2.8371230335920861E-2</v>
+        <v>2.2824536376604851E-2</v>
       </c>
       <c r="X16" s="173">
         <v>0.01</v>
       </c>
       <c r="Y16" s="174">
         <f>SUM(Y4:Y15)</f>
-        <v>14557</v>
+        <v>19628</v>
       </c>
       <c r="Z16" s="167"/>
       <c r="AA16" s="51"/>
@@ -37262,7 +37466,7 @@
       <c r="U18" s="20"/>
       <c r="V18" s="176">
         <f>SUM(V4:V15)/12</f>
-        <v>34.416666666666664</v>
+        <v>37.333333333333336</v>
       </c>
       <c r="W18" s="175" t="e">
         <f>SUM(W4:W15)/12</f>
@@ -37590,7 +37794,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
@@ -37727,8 +37931,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="107">
-        <f>1+1</f>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D4" s="107">
         <v>0</v>
@@ -37762,11 +37965,11 @@
       </c>
       <c r="N4" s="107">
         <f>SUM(B4:M4)</f>
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O4" s="153">
         <f>N4/Q4</f>
-        <v>5.0517807527153326E-4</v>
+        <v>3.0310684516291994E-3</v>
       </c>
       <c r="P4" s="154">
         <v>5.0000000000000001E-3</v>
@@ -37960,32 +38163,56 @@
       <c r="A8" s="106">
         <v>46143</v>
       </c>
-      <c r="B8" s="107"/>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="107"/>
-      <c r="K8" s="107"/>
-      <c r="L8" s="107"/>
-      <c r="M8" s="107"/>
+      <c r="B8" s="107">
+        <v>0</v>
+      </c>
+      <c r="C8" s="107">
+        <v>0</v>
+      </c>
+      <c r="D8" s="103">
+        <v>0</v>
+      </c>
+      <c r="E8" s="103">
+        <v>0</v>
+      </c>
+      <c r="F8" s="107">
+        <v>0</v>
+      </c>
+      <c r="G8" s="107">
+        <v>0</v>
+      </c>
+      <c r="H8" s="107">
+        <v>0</v>
+      </c>
+      <c r="I8" s="107">
+        <v>0</v>
+      </c>
+      <c r="J8" s="107">
+        <v>0</v>
+      </c>
+      <c r="K8" s="107">
+        <v>0</v>
+      </c>
+      <c r="L8" s="107">
+        <v>0</v>
+      </c>
+      <c r="M8" s="107">
+        <v>200</v>
+      </c>
       <c r="N8" s="107">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O8" s="153" t="e">
+        <v>200</v>
+      </c>
+      <c r="O8" s="153">
         <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
+        <v>3.9439952672056793E-2</v>
       </c>
       <c r="P8" s="154">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q8" s="155">
         <f>DADOS!E7</f>
-        <v>0</v>
+        <v>5071</v>
       </c>
       <c r="R8" s="82"/>
       <c r="S8" s="51"/>
@@ -38246,7 +38473,7 @@
       </c>
       <c r="C16" s="83">
         <f t="shared" si="3"/>
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D16" s="83">
         <f t="shared" si="3"/>
@@ -38283,22 +38510,22 @@
       <c r="L16" s="83"/>
       <c r="M16" s="83">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>211</v>
       </c>
       <c r="N16" s="83">
         <f t="shared" si="3"/>
-        <v>68</v>
+        <v>278</v>
       </c>
       <c r="O16" s="156">
         <f>SUM(N16/Q16)</f>
-        <v>4.6712921618465341E-3</v>
+        <v>1.4163439983696759E-2</v>
       </c>
       <c r="P16" s="154">
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="Q16" s="155">
         <f>SUM(Q4:Q15)</f>
-        <v>14557</v>
+        <v>19628</v>
       </c>
       <c r="R16" s="82"/>
       <c r="S16" s="32"/>
@@ -38344,7 +38571,7 @@
       </c>
       <c r="N18" s="87">
         <f>SUM(N4:N15)/12</f>
-        <v>5.666666666666667</v>
+        <v>23.166666666666668</v>
       </c>
       <c r="O18" s="158" t="e">
         <f>SUM(O4:O15)/12</f>
@@ -38510,7 +38737,7 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3" tint="0.59999389629810485"/>
   </sheetPr>
@@ -38672,15 +38899,27 @@
       <c r="B9" s="165" t="s">
         <v>52</v>
       </c>
-      <c r="C9" s="165"/>
-      <c r="D9" s="165"/>
-      <c r="E9" s="165"/>
-      <c r="F9" s="165"/>
-      <c r="G9" s="165"/>
-      <c r="H9" s="165"/>
+      <c r="C9" s="165">
+        <v>12</v>
+      </c>
+      <c r="D9" s="165">
+        <v>0</v>
+      </c>
+      <c r="E9" s="165">
+        <v>0</v>
+      </c>
+      <c r="F9" s="165">
+        <v>0</v>
+      </c>
+      <c r="G9" s="165">
+        <v>0</v>
+      </c>
+      <c r="H9" s="165">
+        <v>0</v>
+      </c>
       <c r="I9" s="165">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="2:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -38794,7 +39033,7 @@
       </c>
       <c r="C17" s="165">
         <f>SUM(C5:C16)</f>
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="D17" s="165">
         <f t="shared" ref="D17:I17" si="1">SUM(D5:D16)</f>
@@ -38818,7 +39057,7 @@
       </c>
       <c r="I17" s="165">
         <f t="shared" si="1"/>
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
